--- a/inst/templates/Reports.xlsx
+++ b/inst/templates/Reports.xlsx
@@ -1,60 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="9"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" firstSheet="0" activeTab="9"/>
   </bookViews>
   <sheets>
-    <sheet name="Scenarios" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="DataGroups" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Outputs" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="ModelParameter" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="TimeProfiles" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="TimeRange" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="PKParameter_Boxplot" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="PKParameter_Forest" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="Histograms" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="DistributionVsRange" sheetId="10" state="visible" r:id="rId12"/>
-    <sheet name="SensitivityPlots" sheetId="11" state="visible" r:id="rId13"/>
-    <sheet name="_Validity" sheetId="12" state="hidden" r:id="rId14"/>
+    <sheet name="Scenarios" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="DataGroups" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Outputs" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ModelParameter" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="TimeProfiles" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="TimeRange" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="PKParameter_Boxplot" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="PKParameter_Forest" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Histograms" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="DistributionVsRange" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="SensitivityPlots" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="_Validity" sheetId="12" state="hidden" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" name="validity_DataGroups_Shape_10" vbProcedure="false">_Validity!$A$2:$A$23</definedName>
-    <definedName function="false" hidden="false" name="validity_DistributionVsRange_FacetScale_112" vbProcedure="false">_Validity!$A$96:$A$99</definedName>
-    <definedName function="false" hidden="false" name="validity_DistributionVsRange_ModeOfBinning_106" vbProcedure="false">_Validity!$A$88:$A$90</definedName>
-    <definedName function="false" hidden="false" name="validity_DistributionVsRange_yScale_109" vbProcedure="false">_Validity!$A$92:$A$94</definedName>
-    <definedName function="false" hidden="false" name="validity_Histograms_FacetScale_96" vbProcedure="false">_Validity!$A$83:$A$86</definedName>
-    <definedName function="false" hidden="false" name="validity_Histograms_xScale_93" vbProcedure="false">_Validity!$A$79:$A$81</definedName>
-    <definedName function="false" hidden="false" name="validity_PKParameter_Boxplot_FacetScale_67" vbProcedure="false">_Validity!$A$59:$A$62</definedName>
-    <definedName function="false" hidden="false" name="validity_PKParameter_Boxplot_Plot_Absolute_68" vbProcedure="false">_Validity!$A$64:$A$65</definedName>
-    <definedName function="false" hidden="false" name="validity_PKParameter_Boxplot_Plot_Ratio_69" vbProcedure="false">_Validity!$A$67:$A$68</definedName>
-    <definedName function="false" hidden="false" name="validity_PKParameter_Boxplot_yScale_64" vbProcedure="false">_Validity!$A$55:$A$57</definedName>
-    <definedName function="false" hidden="false" name="validity_PKParameter_Forest_FacetScale_83" vbProcedure="false">_Validity!$A$74:$A$77</definedName>
-    <definedName function="false" hidden="false" name="validity_PKParameter_Forest_xScale_80" vbProcedure="false">_Validity!$A$70:$A$72</definedName>
-    <definedName function="false" hidden="false" name="validity_TimeProfiles_FacetScale_41" vbProcedure="false">_Validity!$A$32:$A$35</definedName>
-    <definedName function="false" hidden="false" name="validity_TimeProfiles_Plot_PredictedVsObserved_45" vbProcedure="false">_Validity!$A$40:$A$41</definedName>
-    <definedName function="false" hidden="false" name="validity_TimeProfiles_Plot_QQ_50" vbProcedure="false">_Validity!$A$52:$A$53</definedName>
-    <definedName function="false" hidden="false" name="validity_TimeProfiles_Plot_ResidualsAsHistogram_47" vbProcedure="false">_Validity!$A$43:$A$44</definedName>
-    <definedName function="false" hidden="false" name="validity_TimeProfiles_Plot_ResidualsVsObserved_49" vbProcedure="false">_Validity!$A$49:$A$50</definedName>
-    <definedName function="false" hidden="false" name="validity_TimeProfiles_Plot_ResidualsVsTime_48" vbProcedure="false">_Validity!$A$46:$A$47</definedName>
-    <definedName function="false" hidden="false" name="validity_TimeProfiles_Plot_TimeProfiles_42" vbProcedure="false">_Validity!$A$37:$A$38</definedName>
-    <definedName function="false" hidden="false" name="validity_TimeProfiles_SplitPlotsPerTimeRange_39" vbProcedure="false">_Validity!$A$29:$A$30</definedName>
-    <definedName function="false" hidden="false" name="validity_TimeProfiles_yScale_38" vbProcedure="false">_Validity!$A$25:$A$27</definedName>
+    <definedName name="validity_shapeValues">'_Validity'!$A$1:$A$22</definedName>
+    <definedName name="validity_axisScaleValues">'_Validity'!$A$24:$A$26</definedName>
+    <definedName name="validity_yesNoValues">'_Validity'!$A$28:$A$29</definedName>
+    <definedName name="validity_facetScaleValues">'_Validity'!$A$31:$A$34</definedName>
+    <definedName name="validity_modeOfBinningValues">'_Validity'!$A$36:$A$38</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="206">
   <si>
     <t xml:space="preserve">Scenario</t>
   </si>
@@ -677,12 +655,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -691,50 +669,27 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <b/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i val="true"/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i val="true"/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <i/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <i/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="5">
@@ -764,7 +719,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -772,105 +727,76 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="16">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment textRotation="0" horizontal="center" vertical="bottom" indent="0" wrapText="1"/>
+      <protection hidden="0" locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment textRotation="0" horizontal="center" vertical="top" indent="0" wrapText="1"/>
+      <protection hidden="0" locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment textRotation="0" horizontal="center" vertical="bottom" indent="0"/>
+      <protection hidden="0" locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment textRotation="0" horizontal="center" vertical="top" indent="0" wrapText="1"/>
+      <protection hidden="0" locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment textRotation="0" horizontal="general" vertical="bottom" indent="0"/>
+      <protection hidden="0" locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment textRotation="0" horizontal="left" vertical="bottom" indent="0"/>
+      <protection hidden="0" locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment textRotation="0" horizontal="general" vertical="bottom" indent="0" wrapText="1"/>
+      <protection hidden="0" locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment textRotation="0" horizontal="center" vertical="bottom" indent="0"/>
+      <protection hidden="0" locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment textRotation="0" horizontal="center" vertical="bottom" indent="0" wrapText="1"/>
+      <protection hidden="0" locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment textRotation="0" horizontal="center" vertical="bottom" indent="0" wrapText="1"/>
+      <protection hidden="0" locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment textRotation="0" horizontal="center" vertical="top" indent="0"/>
+      <protection hidden="0" locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment textRotation="0" horizontal="center" vertical="top" indent="0" wrapText="1"/>
+      <protection hidden="0" locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment textRotation="0" horizontal="general" vertical="bottom" indent="0" wrapText="1"/>
+      <protection hidden="0" locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment textRotation="0" horizontal="center" vertical="bottom" indent="0" wrapText="1"/>
+      <protection hidden="0" locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment textRotation="0" horizontal="general" vertical="bottom" indent="0"/>
+      <protection hidden="0" locked="0"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -1107,19 +1033,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="10.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="27.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="27.71"/>
+    <col min="1" max="1" width="26.86" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="2" max="2" width="27.42" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="3" max="3" width="27.71" hidden="false" outlineLevel="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1130,7 +1056,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1142,43 +1068,46 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.597222222222222" bottom="0.597222222222222" header="0.511805555555556" footer="0.511805555555556"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
+  <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="0">
+    <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
+    <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD40"/>
-  <sheetFormatPr defaultColWidth="10.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="21.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="19.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="22.81"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="35.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="8" style="0" width="16.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="11.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="23.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="9.57"/>
+    <col min="3" max="3" width="22.42" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="4" max="4" width="21.14" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="5" max="5" width="19.14" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="6" max="6" width="22.81" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="7" max="7" width="35.43" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="8" max="8" width="16.43" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="9" max="9" width="16.43" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="10" max="10" width="16.43" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="11" max="11" width="16.43" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="12" max="12" width="16.43" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="13" max="13" width="11.43" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="14" max="14" width="23.86" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="15" max="15" width="9.57" hidden="false" outlineLevel="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
+    <row r="1" ht="23.25" customHeight="1">
+      <c r="A1" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="9" t="s">
         <v>56</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -1187,37 +1116,37 @@
       <c r="E1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="L1" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="N1" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="O1" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="P1" s="9" t="s">
         <v>73</v>
       </c>
       <c r="Q1" s="15"/>
@@ -1225,11 +1154,11 @@
       <c r="S1" s="15"/>
       <c r="XFD1" s="5"/>
     </row>
-    <row r="2" customFormat="false" ht="52.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" ht="52.5" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="11" t="s">
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -1276,168 +1205,243 @@
       </c>
       <c r="XFD2" s="5"/>
     </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" ht="13.5" customHeight="1">
       <c r="M3" s="7"/>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" ht="13.5" customHeight="1">
       <c r="M4" s="7"/>
     </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" ht="13.5" customHeight="1">
       <c r="M5" s="7"/>
     </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" ht="13.5" customHeight="1">
       <c r="M6" s="7"/>
     </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" ht="13.5" customHeight="1">
       <c r="M7" s="7"/>
     </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" ht="13.5" customHeight="1">
       <c r="M8" s="7"/>
     </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" ht="13.5" customHeight="1">
       <c r="M9" s="7"/>
     </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" ht="13.5" customHeight="1">
       <c r="M10" s="7"/>
     </row>
-    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" ht="13.5" customHeight="1">
       <c r="M11" s="7"/>
     </row>
-    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" ht="13.5" customHeight="1">
       <c r="M12" s="7"/>
     </row>
-    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" ht="13.5" customHeight="1">
       <c r="M13" s="7"/>
     </row>
-    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" ht="13.5" customHeight="1">
       <c r="M14" s="7"/>
     </row>
-    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" ht="13.5" customHeight="1">
       <c r="M15" s="7"/>
     </row>
-    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" ht="13.5" customHeight="1">
       <c r="M16" s="7"/>
     </row>
-    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" ht="13.5" customHeight="1">
       <c r="M17" s="7"/>
     </row>
-    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" ht="13.5" customHeight="1">
       <c r="M18" s="7"/>
     </row>
-    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" ht="13.5" customHeight="1">
       <c r="M19" s="7"/>
     </row>
-    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" ht="13.5" customHeight="1">
       <c r="M20" s="7"/>
     </row>
-    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" ht="13.5" customHeight="1">
       <c r="M21" s="7"/>
     </row>
-    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" ht="13.5" customHeight="1">
       <c r="M22" s="7"/>
     </row>
-    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" ht="13.5" customHeight="1">
       <c r="M23" s="7"/>
     </row>
-    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" ht="13.5" customHeight="1">
       <c r="M24" s="7"/>
     </row>
-    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" ht="13.5" customHeight="1">
       <c r="M25" s="7"/>
     </row>
-    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" ht="13.5" customHeight="1">
       <c r="M26" s="7"/>
     </row>
-    <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" ht="13.5" customHeight="1">
       <c r="M27" s="7"/>
     </row>
-    <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" ht="13.5" customHeight="1">
       <c r="M28" s="7"/>
     </row>
-    <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" ht="13.5" customHeight="1">
       <c r="M29" s="7"/>
     </row>
-    <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" ht="13.5" customHeight="1">
       <c r="M30" s="7"/>
     </row>
-    <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" ht="13.5" customHeight="1">
       <c r="M31" s="7"/>
     </row>
-    <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" ht="13.5" customHeight="1">
       <c r="M32" s="7"/>
     </row>
-    <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" ht="13.5" customHeight="1">
       <c r="M33" s="7"/>
     </row>
-    <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" ht="13.5" customHeight="1">
       <c r="M34" s="7"/>
     </row>
-    <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="35" ht="13.5" customHeight="1">
       <c r="M35" s="7"/>
     </row>
-    <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" ht="13.5" customHeight="1">
       <c r="M36" s="7"/>
     </row>
-    <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="37" ht="13.5" customHeight="1">
       <c r="M37" s="7"/>
     </row>
-    <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="38" ht="13.5" customHeight="1">
       <c r="M38" s="7"/>
     </row>
-    <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="39" ht="13.5" customHeight="1">
       <c r="M39" s="7"/>
     </row>
-    <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" ht="13.5" customHeight="1">
       <c r="M40" s="7"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="J2:J1002" type="list">
-      <formula1>validity_DistributionVsRange_ModeOfBinning_106</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="M2:M1002" type="list">
-      <formula1>validity_DistributionVsRange_yScale_109</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="P2:P1002" type="list">
-      <formula1>validity_DistributionVsRange_FacetScale_112</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.597222222222222" bottom="0.597222222222222" header="0.511805555555556" footer="0.511805555555556"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
+  <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="0">
+    <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
+    <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
   </headerFooter>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_DistributionVsRange_ModeOfBinning_106</xm:f>
+          </x14:formula1>
+          <xm:sqref>J2:J1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_DistributionVsRange_yScale_109</xm:f>
+          </x14:formula1>
+          <xm:sqref>M2:M1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_DistributionVsRange_FacetScale_112</xm:f>
+          </x14:formula1>
+          <xm:sqref>P2:P1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_DistributionVsRange_ModeOfBinning_106</xm:f>
+          </x14:formula1>
+          <xm:sqref>J2:J1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_DistributionVsRange_yScale_109</xm:f>
+          </x14:formula1>
+          <xm:sqref>M2:M1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_DistributionVsRange_FacetScale_112</xm:f>
+          </x14:formula1>
+          <xm:sqref>P2:P1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_DistributionVsRange_ModeOfBinning_106</xm:f>
+          </x14:formula1>
+          <xm:sqref>J2:J1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_DistributionVsRange_yScale_109</xm:f>
+          </x14:formula1>
+          <xm:sqref>M2:M1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_DistributionVsRange_FacetScale_112</xm:f>
+          </x14:formula1>
+          <xm:sqref>P2:P1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_modeOfBinningValues</xm:f>
+          </x14:formula1>
+          <xm:sqref>J2:J1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_axisScaleValues</xm:f>
+          </x14:formula1>
+          <xm:sqref>M2:M1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_facetScaleValues</xm:f>
+          </x14:formula1>
+          <xm:sqref>P2:P1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultColWidth="10.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="24.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="46"/>
+    <col min="3" max="3" width="24.86" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="5" max="5" width="16.43" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="6" max="6" width="14" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="7" max="7" width="13.86" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="8" max="8" width="46" hidden="false" outlineLevel="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
+    <row r="1" ht="23.25" customHeight="1">
+      <c r="A1" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="9" t="s">
         <v>56</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -1455,15 +1459,15 @@
       <c r="H1" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" ht="51" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="11" t="s">
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -1489,448 +1493,219 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.597222222222222" bottom="0.597222222222222" header="0.511805555555556" footer="0.511805555555556"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
+  <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="0">
+    <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
+    <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:A99"/>
-  <sheetFormatPr defaultColWidth="10.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="45.71"/>
+    <col min="1" max="1" width="45.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="1">
+      <c r="A1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+    <row r="2">
+      <c r="A2" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+    <row r="3">
+      <c r="A3" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="4">
+      <c r="A4" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="5">
+      <c r="A5" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+    <row r="6">
+      <c r="A6" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+    <row r="7">
+      <c r="A7" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+    <row r="8">
+      <c r="A8" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+    <row r="9">
+      <c r="A9" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+    <row r="10">
+      <c r="A10" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+    <row r="11">
+      <c r="A11" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+    <row r="12">
+      <c r="A12" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+    <row r="13">
+      <c r="A13" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+    <row r="14">
+      <c r="A14" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+    <row r="15">
+      <c r="A15" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+    <row r="16">
+      <c r="A16" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+    <row r="17">
+      <c r="A17" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+    <row r="18">
+      <c r="A18" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+    <row r="19">
+      <c r="A19" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+    <row r="20">
+      <c r="A20" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+    <row r="21">
+      <c r="A21" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+    <row r="22">
+      <c r="A22" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+    <row r="24">
+      <c r="A24" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+    <row r="25">
+      <c r="A25" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+    <row r="26">
+      <c r="A26" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+    <row r="28">
+      <c r="A28" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+    <row r="29">
+      <c r="A29" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+    <row r="31">
+      <c r="A31" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+    <row r="32">
+      <c r="A32" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+    <row r="33">
+      <c r="A33" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+    <row r="34">
+      <c r="A34" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="0" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="0" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="0" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="0" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="0" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="0" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="0" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="0" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="0" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="0" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="0" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="0" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="0" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="0" t="s">
+    <row r="36">
+      <c r="A36" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="0" t="s">
+    <row r="37">
+      <c r="A37" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="0" t="s">
+    <row r="38">
+      <c r="A38" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="0" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="0" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="0" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="0" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="0" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="0" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="0" t="s">
-        <v>202</v>
-      </c>
-    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultColWidth="10.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="23.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="29.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16382" style="0" width="11.53"/>
+    <col min="1" max="1" width="23.14" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="2" max="2" width="23.14" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="3" max="3" width="23.14" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="4" max="4" width="29.42" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="5" max="5" width="29.42" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="6" max="6" width="17" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="16382" max="16382" width="11.53" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="16383" max="16383" width="11.53" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="16384" max="16384" width="11.53" hidden="false" outlineLevel="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" ht="15" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
@@ -1953,7 +1728,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" ht="57.75" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>13</v>
       </c>
@@ -1979,43 +1754,78 @@
       <c r="I2" s="5"/>
       <c r="J2" s="5"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" ht="15" customHeight="1">
       <c r="A3" s="6"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="G2:G1002" type="list">
-      <formula1>validity_DataGroups_Shape_10</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.634722222222222" bottom="0.634722222222222" header="0.511805555555556" footer="0.511805555555556"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
+  <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="0">
+    <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
+    <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
   </headerFooter>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_DataGroups_Shape_10</xm:f>
+          </x14:formula1>
+          <xm:sqref>G2:G1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_DataGroups_Shape_10</xm:f>
+          </x14:formula1>
+          <xm:sqref>G2:G1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_DataGroups_Shape_10</xm:f>
+          </x14:formula1>
+          <xm:sqref>G2:G1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_shapeValues</xm:f>
+          </x14:formula1>
+          <xm:sqref>G2:G1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="10.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="19.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="26.71"/>
+    <col min="1" max="1" width="16.29" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="2" max="2" width="14.86" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="3" max="3" width="12.71" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="4" max="4" width="11.29" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="5" max="5" width="19.57" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="6" max="6" width="26.71" hidden="false" outlineLevel="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" ht="15" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>19</v>
       </c>
@@ -2035,7 +1845,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" ht="45.75" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>24</v>
       </c>
@@ -2056,29 +1866,28 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.597222222222222" bottom="0.597222222222222" header="0.511805555555556" footer="0.511805555555556"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
+  <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="0">
+    <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
+    <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="10.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.69"/>
+    <col min="2" max="2" width="18.08" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="3" max="3" width="16.69" hidden="false" outlineLevel="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" ht="13.5" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>30</v>
       </c>
@@ -2092,7 +1901,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" ht="34.5" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>32</v>
       </c>
@@ -2106,7 +1915,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" ht="13.5" customHeight="1">
       <c r="A3" s="5" t="s">
         <v>35</v>
       </c>
@@ -2120,7 +1929,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" ht="13.5" customHeight="1">
       <c r="A4" s="5" t="s">
         <v>38</v>
       </c>
@@ -2134,7 +1943,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" ht="13.5" customHeight="1">
       <c r="A5" s="5" t="s">
         <v>42</v>
       </c>
@@ -2148,7 +1957,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" ht="13.5" customHeight="1">
       <c r="A6" s="5" t="s">
         <v>45</v>
       </c>
@@ -2159,7 +1968,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" ht="13.5" customHeight="1">
       <c r="A7" s="5" t="s">
         <v>47</v>
       </c>
@@ -2173,7 +1982,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" ht="13.5" customHeight="1">
       <c r="A8" s="5" t="s">
         <v>50</v>
       </c>
@@ -2188,40 +1997,40 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="0">
+    <oddHeader>&amp;L&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A&amp;R</oddHeader>
+    <oddFooter>&amp;L&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P&amp;R</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AD40"/>
-  <sheetFormatPr defaultColWidth="10.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="16.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="19.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="9.57"/>
+    <col min="3" max="3" width="17.71" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="5" max="5" width="16.43" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="6" max="6" width="16.43" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="10" max="10" width="18" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="12" max="12" width="18" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="14" max="14" width="19.14" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="24" max="24" width="9.57" hidden="false" outlineLevel="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
+    <row r="1" ht="45" customHeight="1">
+      <c r="A1" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="9" t="s">
         <v>56</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -2239,22 +2048,22 @@
       <c r="H1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="K1" s="10" t="s">
         <v>63</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="M1" s="11" t="s">
+      <c r="M1" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="N1" s="9" t="s">
         <v>66</v>
       </c>
       <c r="O1" s="1" t="s">
@@ -2266,51 +2075,51 @@
       <c r="Q1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="R1" s="10" t="s">
+      <c r="R1" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="S1" s="10" t="s">
+      <c r="S1" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="T1" s="10" t="s">
+      <c r="T1" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="U1" s="10" t="s">
+      <c r="U1" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="V1" s="10" t="s">
+      <c r="V1" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="W1" s="10" t="s">
+      <c r="W1" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="X1" s="10" t="s">
+      <c r="X1" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="Y1" s="10" t="s">
+      <c r="Y1" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="Z1" s="10" t="s">
+      <c r="Z1" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="AA1" s="10" t="s">
+      <c r="AA1" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="AB1" s="10" t="s">
+      <c r="AB1" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="AC1" s="10" t="s">
+      <c r="AC1" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="AD1" s="10" t="s">
+      <c r="AD1" s="9" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="59.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" ht="59.25" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="11" t="s">
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -2337,13 +2146,13 @@
       <c r="J2" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="K2" s="13" t="s">
+      <c r="K2" s="12" t="s">
         <v>93</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="M2" s="13" t="s">
+      <c r="M2" s="12" t="s">
         <v>95</v>
       </c>
       <c r="N2" s="2" t="s">
@@ -2358,7 +2167,7 @@
       <c r="Q2" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="R2" s="13" t="s">
+      <c r="R2" s="12" t="s">
         <v>100</v>
       </c>
       <c r="S2" s="2" t="s">
@@ -2398,263 +2207,458 @@
         <v>112</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
+    <row r="3" ht="15" customHeight="1">
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
       <c r="R3" s="7"/>
       <c r="S3" s="7"/>
       <c r="T3" s="7"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" ht="15" customHeight="1">
       <c r="R4" s="7"/>
       <c r="S4" s="7"/>
       <c r="T4" s="7"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" ht="15" customHeight="1">
       <c r="R5" s="7"/>
       <c r="S5" s="7"/>
       <c r="T5" s="7"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" ht="15" customHeight="1">
       <c r="R6" s="7"/>
       <c r="S6" s="7"/>
       <c r="T6" s="7"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" ht="15" customHeight="1">
       <c r="R7" s="7"/>
       <c r="S7" s="7"/>
       <c r="T7" s="7"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" ht="15" customHeight="1">
       <c r="R8" s="7"/>
       <c r="S8" s="7"/>
       <c r="T8" s="7"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" ht="15" customHeight="1">
       <c r="R9" s="7"/>
       <c r="S9" s="7"/>
       <c r="T9" s="7"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" ht="15" customHeight="1">
       <c r="R10" s="7"/>
       <c r="S10" s="7"/>
       <c r="T10" s="7"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" ht="15" customHeight="1">
       <c r="R11" s="7"/>
       <c r="S11" s="7"/>
       <c r="T11" s="7"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" ht="15" customHeight="1">
       <c r="R12" s="7"/>
       <c r="S12" s="7"/>
       <c r="T12" s="7"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" ht="15" customHeight="1">
       <c r="R13" s="7"/>
       <c r="S13" s="7"/>
       <c r="T13" s="7"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" ht="15" customHeight="1">
       <c r="R14" s="7"/>
       <c r="S14" s="7"/>
       <c r="T14" s="7"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" ht="15" customHeight="1">
       <c r="R15" s="7"/>
       <c r="S15" s="7"/>
       <c r="T15" s="7"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" ht="15" customHeight="1">
       <c r="R16" s="7"/>
       <c r="S16" s="7"/>
       <c r="T16" s="7"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" ht="15" customHeight="1">
       <c r="R17" s="7"/>
       <c r="S17" s="7"/>
       <c r="T17" s="7"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" ht="15" customHeight="1">
       <c r="R18" s="7"/>
       <c r="S18" s="7"/>
       <c r="T18" s="7"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" ht="15" customHeight="1">
       <c r="R19" s="7"/>
       <c r="S19" s="7"/>
       <c r="T19" s="7"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" ht="15" customHeight="1">
       <c r="R20" s="7"/>
       <c r="S20" s="7"/>
       <c r="T20" s="7"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" ht="15" customHeight="1">
       <c r="R21" s="7"/>
       <c r="S21" s="7"/>
       <c r="T21" s="7"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" ht="15" customHeight="1">
       <c r="R22" s="7"/>
       <c r="S22" s="7"/>
       <c r="T22" s="7"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" ht="15" customHeight="1">
       <c r="R23" s="7"/>
       <c r="S23" s="7"/>
       <c r="T23" s="7"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" ht="15" customHeight="1">
       <c r="R24" s="7"/>
       <c r="S24" s="7"/>
       <c r="T24" s="7"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" ht="15" customHeight="1">
       <c r="R25" s="7"/>
       <c r="S25" s="7"/>
       <c r="T25" s="7"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" ht="15" customHeight="1">
       <c r="R26" s="7"/>
       <c r="S26" s="7"/>
       <c r="T26" s="7"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" ht="15" customHeight="1">
       <c r="R27" s="7"/>
       <c r="S27" s="7"/>
       <c r="T27" s="7"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" ht="15" customHeight="1">
       <c r="R28" s="7"/>
       <c r="S28" s="7"/>
       <c r="T28" s="7"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" ht="15" customHeight="1">
       <c r="R29" s="7"/>
       <c r="S29" s="7"/>
       <c r="T29" s="7"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" ht="15" customHeight="1">
       <c r="R30" s="7"/>
       <c r="S30" s="7"/>
       <c r="T30" s="7"/>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" ht="15" customHeight="1">
       <c r="R31" s="7"/>
       <c r="S31" s="7"/>
       <c r="T31" s="7"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" ht="15" customHeight="1">
       <c r="R32" s="7"/>
       <c r="S32" s="7"/>
       <c r="T32" s="7"/>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" ht="15" customHeight="1">
       <c r="R33" s="7"/>
       <c r="S33" s="7"/>
       <c r="T33" s="7"/>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" ht="15" customHeight="1">
       <c r="R34" s="7"/>
       <c r="S34" s="7"/>
       <c r="T34" s="7"/>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="35" ht="15" customHeight="1">
       <c r="R35" s="7"/>
       <c r="S35" s="7"/>
       <c r="T35" s="7"/>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" ht="15" customHeight="1">
       <c r="R36" s="7"/>
       <c r="S36" s="7"/>
       <c r="T36" s="7"/>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="37" ht="15" customHeight="1">
       <c r="R37" s="7"/>
       <c r="S37" s="7"/>
       <c r="T37" s="7"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="38" ht="15" customHeight="1">
       <c r="R38" s="7"/>
       <c r="S38" s="7"/>
       <c r="T38" s="7"/>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="39" ht="15" customHeight="1">
       <c r="R39" s="7"/>
       <c r="S39" s="7"/>
       <c r="T39" s="7"/>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" ht="15" customHeight="1">
       <c r="R40" s="7"/>
       <c r="S40" s="7"/>
       <c r="T40" s="7"/>
     </row>
   </sheetData>
-  <dataValidations count="9">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="R2:R1002" type="list">
-      <formula1>validity_TimeProfiles_yScale_38</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="S2:S1002" type="list">
-      <formula1>validity_TimeProfiles_SplitPlotsPerTimeRange_39</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="U2:U1002" type="list">
-      <formula1>validity_TimeProfiles_FacetScale_41</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="V2:V1002" type="list">
-      <formula1>validity_TimeProfiles_Plot_TimeProfiles_42</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="Y2:Y1002" type="list">
-      <formula1>validity_TimeProfiles_Plot_PredictedVsObserved_45</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="AA2:AA1002" type="list">
-      <formula1>validity_TimeProfiles_Plot_ResidualsAsHistogram_47</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="AB2:AB1002" type="list">
-      <formula1>validity_TimeProfiles_Plot_ResidualsVsTime_48</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="AC2:AC1002" type="list">
-      <formula1>validity_TimeProfiles_Plot_ResidualsVsObserved_49</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="AD2:AD1002" type="list">
-      <formula1>validity_TimeProfiles_Plot_QQ_50</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.597222222222222" bottom="0.597222222222222" header="0.511805555555556" footer="0.511805555555556"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
+  <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="0">
+    <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
+    <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
   </headerFooter>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="9">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_TimeProfiles_yScale_38</xm:f>
+          </x14:formula1>
+          <xm:sqref>R2:R1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_TimeProfiles_SplitPlotsPerTimeRange_39</xm:f>
+          </x14:formula1>
+          <xm:sqref>S2:S1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_TimeProfiles_FacetScale_41</xm:f>
+          </x14:formula1>
+          <xm:sqref>U2:U1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_TimeProfiles_Plot_TimeProfiles_42</xm:f>
+          </x14:formula1>
+          <xm:sqref>V2:V1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_TimeProfiles_Plot_PredictedVsObserved_45</xm:f>
+          </x14:formula1>
+          <xm:sqref>Y2:Y1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_TimeProfiles_Plot_ResidualsAsHistogram_47</xm:f>
+          </x14:formula1>
+          <xm:sqref>AA2:AA1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_TimeProfiles_Plot_ResidualsVsTime_48</xm:f>
+          </x14:formula1>
+          <xm:sqref>AB2:AB1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_TimeProfiles_Plot_ResidualsVsObserved_49</xm:f>
+          </x14:formula1>
+          <xm:sqref>AC2:AC1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_TimeProfiles_Plot_QQ_50</xm:f>
+          </x14:formula1>
+          <xm:sqref>AD2:AD1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="9">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_TimeProfiles_yScale_38</xm:f>
+          </x14:formula1>
+          <xm:sqref>R2:R1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_TimeProfiles_SplitPlotsPerTimeRange_39</xm:f>
+          </x14:formula1>
+          <xm:sqref>S2:S1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_TimeProfiles_FacetScale_41</xm:f>
+          </x14:formula1>
+          <xm:sqref>U2:U1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_TimeProfiles_Plot_TimeProfiles_42</xm:f>
+          </x14:formula1>
+          <xm:sqref>V2:V1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_TimeProfiles_Plot_PredictedVsObserved_45</xm:f>
+          </x14:formula1>
+          <xm:sqref>Y2:Y1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_TimeProfiles_Plot_ResidualsAsHistogram_47</xm:f>
+          </x14:formula1>
+          <xm:sqref>AA2:AA1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_TimeProfiles_Plot_ResidualsVsTime_48</xm:f>
+          </x14:formula1>
+          <xm:sqref>AB2:AB1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_TimeProfiles_Plot_ResidualsVsObserved_49</xm:f>
+          </x14:formula1>
+          <xm:sqref>AC2:AC1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_TimeProfiles_Plot_QQ_50</xm:f>
+          </x14:formula1>
+          <xm:sqref>AD2:AD1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="9">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_TimeProfiles_yScale_38</xm:f>
+          </x14:formula1>
+          <xm:sqref>R2:R1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_TimeProfiles_SplitPlotsPerTimeRange_39</xm:f>
+          </x14:formula1>
+          <xm:sqref>S2:S1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_TimeProfiles_FacetScale_41</xm:f>
+          </x14:formula1>
+          <xm:sqref>U2:U1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_TimeProfiles_Plot_TimeProfiles_42</xm:f>
+          </x14:formula1>
+          <xm:sqref>V2:V1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_TimeProfiles_Plot_PredictedVsObserved_45</xm:f>
+          </x14:formula1>
+          <xm:sqref>Y2:Y1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_TimeProfiles_Plot_ResidualsAsHistogram_47</xm:f>
+          </x14:formula1>
+          <xm:sqref>AA2:AA1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_TimeProfiles_Plot_ResidualsVsTime_48</xm:f>
+          </x14:formula1>
+          <xm:sqref>AB2:AB1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_TimeProfiles_Plot_ResidualsVsObserved_49</xm:f>
+          </x14:formula1>
+          <xm:sqref>AC2:AC1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_TimeProfiles_Plot_QQ_50</xm:f>
+          </x14:formula1>
+          <xm:sqref>AD2:AD1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="9">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_axisScaleValues</xm:f>
+          </x14:formula1>
+          <xm:sqref>R2:R1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_yesNoValues</xm:f>
+          </x14:formula1>
+          <xm:sqref>S2:S1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_facetScaleValues</xm:f>
+          </x14:formula1>
+          <xm:sqref>U2:U1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_yesNoValues</xm:f>
+          </x14:formula1>
+          <xm:sqref>V2:V1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_yesNoValues</xm:f>
+          </x14:formula1>
+          <xm:sqref>Y2:Y1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_yesNoValues</xm:f>
+          </x14:formula1>
+          <xm:sqref>AA2:AA1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_yesNoValues</xm:f>
+          </x14:formula1>
+          <xm:sqref>AB2:AB1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_yesNoValues</xm:f>
+          </x14:formula1>
+          <xm:sqref>AC2:AC1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_yesNoValues</xm:f>
+          </x14:formula1>
+          <xm:sqref>AD2:AD1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="10.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="21.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="25.29"/>
+    <col min="1" max="1" width="11.29" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="2" max="2" width="21.57" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="3" max="3" width="18.29" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="4" max="4" width="25.29" hidden="false" outlineLevel="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>113</v>
       </c>
@@ -2668,7 +2672,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" ht="39.75" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>117</v>
       </c>
@@ -2682,7 +2686,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" ht="15" customHeight="1">
       <c r="A3" s="7" t="s">
         <v>121</v>
       </c>
@@ -2693,7 +2697,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" ht="23.25" customHeight="1">
       <c r="A4" s="7" t="s">
         <v>124</v>
       </c>
@@ -2704,7 +2708,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" ht="23.25" customHeight="1">
       <c r="A5" s="7" t="s">
         <v>126</v>
       </c>
@@ -2716,45 +2720,45 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.597222222222222" bottom="0.597222222222222" header="0.511805555555556" footer="0.511805555555556"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
+  <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="0">
+    <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
+    <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O40"/>
-  <sheetFormatPr defaultColWidth="10.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="21.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="19.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="22.81"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="35.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="16.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="11.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="23.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="9.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="11.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="11.29"/>
+    <col min="3" max="3" width="22.42" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="4" max="4" width="21.14" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="5" max="5" width="19.14" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="6" max="6" width="22.81" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="7" max="7" width="35.43" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="8" max="8" width="16.43" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="9" max="9" width="16.43" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="10" max="10" width="11.43" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="11" max="11" width="23.86" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="12" max="12" width="9.57" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="14" max="14" width="11.43" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="15" max="15" width="11.29" hidden="false" outlineLevel="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
+    <row r="1" ht="23.25" customHeight="1">
+      <c r="A1" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="9" t="s">
         <v>56</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -2763,42 +2767,42 @@
       <c r="E1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="9" t="s">
         <v>129</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="L1" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="N1" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="O1" s="9" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="52.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" ht="52.5" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="11" t="s">
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -2841,177 +2845,273 @@
         <v>140</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" ht="15" customHeight="1">
       <c r="J3" s="7"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" ht="15" customHeight="1">
       <c r="J4" s="7"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" ht="15" customHeight="1">
       <c r="J5" s="7"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" ht="15" customHeight="1">
       <c r="J6" s="7"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" ht="15" customHeight="1">
       <c r="J7" s="7"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" ht="15" customHeight="1">
       <c r="J8" s="7"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" ht="15" customHeight="1">
       <c r="J9" s="7"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" ht="15" customHeight="1">
       <c r="J10" s="7"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" ht="15" customHeight="1">
       <c r="J11" s="7"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" ht="15" customHeight="1">
       <c r="J12" s="7"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" ht="15" customHeight="1">
       <c r="J13" s="7"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" ht="15" customHeight="1">
       <c r="J14" s="7"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" ht="15" customHeight="1">
       <c r="J15" s="7"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" ht="15" customHeight="1">
       <c r="J16" s="7"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" ht="15" customHeight="1">
       <c r="J17" s="7"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" ht="15" customHeight="1">
       <c r="J18" s="7"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" ht="15" customHeight="1">
       <c r="J19" s="7"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" ht="15" customHeight="1">
       <c r="J20" s="7"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" ht="15" customHeight="1">
       <c r="J21" s="7"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" ht="15" customHeight="1">
       <c r="J22" s="7"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" ht="15" customHeight="1">
       <c r="J23" s="7"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" ht="15" customHeight="1">
       <c r="J24" s="7"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" ht="15" customHeight="1">
       <c r="J25" s="7"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" ht="15" customHeight="1">
       <c r="J26" s="7"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" ht="15" customHeight="1">
       <c r="J27" s="7"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" ht="15" customHeight="1">
       <c r="J28" s="7"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" ht="15" customHeight="1">
       <c r="J29" s="7"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" ht="15" customHeight="1">
       <c r="J30" s="7"/>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" ht="15" customHeight="1">
       <c r="J31" s="7"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" ht="15" customHeight="1">
       <c r="J32" s="7"/>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" ht="15" customHeight="1">
       <c r="J33" s="7"/>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" ht="15" customHeight="1">
       <c r="J34" s="7"/>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="35" ht="15" customHeight="1">
       <c r="J35" s="7"/>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" ht="15" customHeight="1">
       <c r="J36" s="7"/>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="37" ht="15" customHeight="1">
       <c r="J37" s="7"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="38" ht="15" customHeight="1">
       <c r="J38" s="7"/>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="39" ht="15" customHeight="1">
       <c r="J39" s="7"/>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" ht="15" customHeight="1">
       <c r="J40" s="7"/>
     </row>
   </sheetData>
-  <dataValidations count="4">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="J2:J1002" type="list">
-      <formula1>validity_PKParameter_Boxplot_yScale_64</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="M2:M1002" type="list">
-      <formula1>validity_PKParameter_Boxplot_FacetScale_67</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="N2:N1002" type="list">
-      <formula1>validity_PKParameter_Boxplot_Plot_Absolute_68</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="O2:O1002" type="list">
-      <formula1>validity_PKParameter_Boxplot_Plot_Ratio_69</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.597222222222222" bottom="0.597222222222222" header="0.511805555555556" footer="0.511805555555556"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
+  <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="0">
+    <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
+    <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
   </headerFooter>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_PKParameter_Boxplot_yScale_64</xm:f>
+          </x14:formula1>
+          <xm:sqref>J2:J1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_PKParameter_Boxplot_FacetScale_67</xm:f>
+          </x14:formula1>
+          <xm:sqref>M2:M1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_PKParameter_Boxplot_Plot_Absolute_68</xm:f>
+          </x14:formula1>
+          <xm:sqref>N2:N1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_PKParameter_Boxplot_Plot_Ratio_69</xm:f>
+          </x14:formula1>
+          <xm:sqref>O2:O1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_PKParameter_Boxplot_yScale_64</xm:f>
+          </x14:formula1>
+          <xm:sqref>J2:J1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_PKParameter_Boxplot_FacetScale_67</xm:f>
+          </x14:formula1>
+          <xm:sqref>M2:M1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_PKParameter_Boxplot_Plot_Absolute_68</xm:f>
+          </x14:formula1>
+          <xm:sqref>N2:N1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_PKParameter_Boxplot_Plot_Ratio_69</xm:f>
+          </x14:formula1>
+          <xm:sqref>O2:O1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_PKParameter_Boxplot_yScale_64</xm:f>
+          </x14:formula1>
+          <xm:sqref>J2:J1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_PKParameter_Boxplot_FacetScale_67</xm:f>
+          </x14:formula1>
+          <xm:sqref>M2:M1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_PKParameter_Boxplot_Plot_Absolute_68</xm:f>
+          </x14:formula1>
+          <xm:sqref>N2:N1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_PKParameter_Boxplot_Plot_Ratio_69</xm:f>
+          </x14:formula1>
+          <xm:sqref>O2:O1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_axisScaleValues</xm:f>
+          </x14:formula1>
+          <xm:sqref>J2:J1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_facetScaleValues</xm:f>
+          </x14:formula1>
+          <xm:sqref>M2:M1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_yesNoValues</xm:f>
+          </x14:formula1>
+          <xm:sqref>N2:N1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_yesNoValues</xm:f>
+          </x14:formula1>
+          <xm:sqref>O2:O1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N40"/>
-  <sheetFormatPr defaultColWidth="10.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="21.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="19.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="35.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="16.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="9.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="11.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="23.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="9.57"/>
+    <col min="3" max="3" width="22.42" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="4" max="4" width="14.14" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="5" max="5" width="21.14" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="6" max="6" width="19.14" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="7" max="7" width="35.43" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="8" max="8" width="16.43" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="9" max="9" width="16.43" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="10" max="10" width="9.86" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="11" max="11" width="11.43" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="12" max="12" width="23.86" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="13" max="13" width="9.57" hidden="false" outlineLevel="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
+    <row r="1" ht="23.25" customHeight="1">
+      <c r="A1" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="9" t="s">
         <v>56</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -3023,36 +3123,36 @@
       <c r="F1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="9" t="s">
         <v>129</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>61</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="L1" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="N1" s="9" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" ht="49.5" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="11" t="s">
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -3092,169 +3192,227 @@
         <v>103</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" ht="15" customHeight="1">
       <c r="K3" s="7"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" ht="15" customHeight="1">
       <c r="K4" s="7"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" ht="15" customHeight="1">
       <c r="K5" s="7"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" ht="15" customHeight="1">
       <c r="K6" s="7"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" ht="15" customHeight="1">
       <c r="K7" s="7"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" ht="15" customHeight="1">
       <c r="K8" s="7"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" ht="15" customHeight="1">
       <c r="K9" s="7"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" ht="15" customHeight="1">
       <c r="K10" s="7"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" ht="15" customHeight="1">
       <c r="K11" s="7"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" ht="15" customHeight="1">
       <c r="K12" s="7"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" ht="15" customHeight="1">
       <c r="K13" s="7"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" ht="15" customHeight="1">
       <c r="K14" s="7"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" ht="15" customHeight="1">
       <c r="K15" s="7"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" ht="15" customHeight="1">
       <c r="K16" s="7"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" ht="15" customHeight="1">
       <c r="K17" s="7"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" ht="15" customHeight="1">
       <c r="K18" s="7"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" ht="15" customHeight="1">
       <c r="K19" s="7"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" ht="15" customHeight="1">
       <c r="K20" s="7"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" ht="15" customHeight="1">
       <c r="K21" s="7"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" ht="15" customHeight="1">
       <c r="K22" s="7"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" ht="15" customHeight="1">
       <c r="K23" s="7"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" ht="15" customHeight="1">
       <c r="K24" s="7"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" ht="15" customHeight="1">
       <c r="K25" s="7"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" ht="15" customHeight="1">
       <c r="K26" s="7"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" ht="15" customHeight="1">
       <c r="K27" s="7"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" ht="15" customHeight="1">
       <c r="K28" s="7"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" ht="15" customHeight="1">
       <c r="K29" s="7"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" ht="15" customHeight="1">
       <c r="K30" s="7"/>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" ht="15" customHeight="1">
       <c r="K31" s="7"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" ht="15" customHeight="1">
       <c r="K32" s="7"/>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" ht="15" customHeight="1">
       <c r="K33" s="7"/>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" ht="15" customHeight="1">
       <c r="K34" s="7"/>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="35" ht="15" customHeight="1">
       <c r="K35" s="7"/>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" ht="15" customHeight="1">
       <c r="K36" s="7"/>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="37" ht="15" customHeight="1">
       <c r="K37" s="7"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="38" ht="15" customHeight="1">
       <c r="K38" s="7"/>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="39" ht="15" customHeight="1">
       <c r="K39" s="7"/>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" ht="15" customHeight="1">
       <c r="K40" s="7"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="K2:K1002" type="list">
-      <formula1>validity_PKParameter_Forest_xScale_80</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="N2:N1002" type="list">
-      <formula1>validity_PKParameter_Forest_FacetScale_83</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.597222222222222" bottom="0.597222222222222" header="0.511805555555556" footer="0.511805555555556"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
+  <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="0">
+    <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
+    <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
   </headerFooter>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_PKParameter_Forest_xScale_80</xm:f>
+          </x14:formula1>
+          <xm:sqref>K2:K1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_PKParameter_Forest_FacetScale_83</xm:f>
+          </x14:formula1>
+          <xm:sqref>N2:N1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_PKParameter_Forest_xScale_80</xm:f>
+          </x14:formula1>
+          <xm:sqref>K2:K1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_PKParameter_Forest_FacetScale_83</xm:f>
+          </x14:formula1>
+          <xm:sqref>N2:N1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_PKParameter_Forest_xScale_80</xm:f>
+          </x14:formula1>
+          <xm:sqref>K2:K1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_PKParameter_Forest_FacetScale_83</xm:f>
+          </x14:formula1>
+          <xm:sqref>N2:N1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_axisScaleValues</xm:f>
+          </x14:formula1>
+          <xm:sqref>K2:K1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_facetScaleValues</xm:f>
+          </x14:formula1>
+          <xm:sqref>N2:N1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD40"/>
-  <sheetFormatPr defaultColWidth="10.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="21.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="19.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="22.81"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="35.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="16.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="11.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="23.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="9.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16382" style="0" width="11.53"/>
+    <col min="3" max="3" width="22.42" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="4" max="4" width="21.14" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="5" max="5" width="19.14" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="6" max="6" width="22.81" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="7" max="7" width="35.43" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="8" max="8" width="16.43" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="9" max="9" width="16.43" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="10" max="10" width="11.43" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="11" max="11" width="23.86" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="12" max="12" width="9.57" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="16382" max="16382" width="11.53" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="16383" max="16383" width="11.53" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="16384" max="16384" width="11.53" hidden="false" outlineLevel="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
+    <row r="1" ht="23.25" customHeight="1">
+      <c r="A1" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="9" t="s">
         <v>56</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -3263,28 +3421,28 @@
       <c r="E1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="L1" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="9" t="s">
         <v>73</v>
       </c>
       <c r="N1" s="15"/>
@@ -3295,11 +3453,11 @@
       <c r="XFC1" s="5"/>
       <c r="XFD1" s="5"/>
     </row>
-    <row r="2" customFormat="false" ht="52.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" ht="52.5" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="11" t="s">
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -3340,137 +3498,192 @@
       <c r="XFC2" s="5"/>
       <c r="XFD2" s="5"/>
     </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" ht="13.5" customHeight="1">
       <c r="J3" s="7"/>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" ht="13.5" customHeight="1">
       <c r="J4" s="7"/>
     </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" ht="13.5" customHeight="1">
       <c r="J5" s="7"/>
     </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" ht="13.5" customHeight="1">
       <c r="J6" s="7"/>
     </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" ht="13.5" customHeight="1">
       <c r="J7" s="7"/>
     </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" ht="13.5" customHeight="1">
       <c r="J8" s="7"/>
     </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" ht="13.5" customHeight="1">
       <c r="J9" s="7"/>
     </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" ht="13.5" customHeight="1">
       <c r="J10" s="7"/>
     </row>
-    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" ht="13.5" customHeight="1">
       <c r="J11" s="7"/>
     </row>
-    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" ht="13.5" customHeight="1">
       <c r="J12" s="7"/>
     </row>
-    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" ht="13.5" customHeight="1">
       <c r="J13" s="7"/>
     </row>
-    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" ht="13.5" customHeight="1">
       <c r="J14" s="7"/>
     </row>
-    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" ht="13.5" customHeight="1">
       <c r="J15" s="7"/>
     </row>
-    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" ht="13.5" customHeight="1">
       <c r="J16" s="7"/>
     </row>
-    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" ht="13.5" customHeight="1">
       <c r="J17" s="7"/>
     </row>
-    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" ht="13.5" customHeight="1">
       <c r="J18" s="7"/>
     </row>
-    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" ht="13.5" customHeight="1">
       <c r="J19" s="7"/>
     </row>
-    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" ht="13.5" customHeight="1">
       <c r="J20" s="7"/>
     </row>
-    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" ht="13.5" customHeight="1">
       <c r="J21" s="7"/>
     </row>
-    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" ht="13.5" customHeight="1">
       <c r="J22" s="7"/>
     </row>
-    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" ht="13.5" customHeight="1">
       <c r="J23" s="7"/>
     </row>
-    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" ht="13.5" customHeight="1">
       <c r="J24" s="7"/>
     </row>
-    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" ht="13.5" customHeight="1">
       <c r="J25" s="7"/>
     </row>
-    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" ht="13.5" customHeight="1">
       <c r="J26" s="7"/>
     </row>
-    <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" ht="13.5" customHeight="1">
       <c r="J27" s="7"/>
     </row>
-    <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" ht="13.5" customHeight="1">
       <c r="J28" s="7"/>
     </row>
-    <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" ht="13.5" customHeight="1">
       <c r="J29" s="7"/>
     </row>
-    <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" ht="13.5" customHeight="1">
       <c r="J30" s="7"/>
     </row>
-    <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" ht="13.5" customHeight="1">
       <c r="J31" s="7"/>
     </row>
-    <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" ht="13.5" customHeight="1">
       <c r="J32" s="7"/>
     </row>
-    <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" ht="13.5" customHeight="1">
       <c r="J33" s="7"/>
     </row>
-    <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" ht="13.5" customHeight="1">
       <c r="J34" s="7"/>
     </row>
-    <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="35" ht="13.5" customHeight="1">
       <c r="J35" s="7"/>
     </row>
-    <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" ht="13.5" customHeight="1">
       <c r="J36" s="7"/>
     </row>
-    <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="37" ht="13.5" customHeight="1">
       <c r="J37" s="7"/>
     </row>
-    <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="38" ht="13.5" customHeight="1">
       <c r="J38" s="7"/>
     </row>
-    <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="39" ht="13.5" customHeight="1">
       <c r="J39" s="7"/>
     </row>
-    <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" ht="13.5" customHeight="1">
       <c r="J40" s="7"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="J2:J1002" type="list">
-      <formula1>validity_Histograms_xScale_93</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="M2:M1002" type="list">
-      <formula1>validity_Histograms_FacetScale_96</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.597222222222222" bottom="0.597222222222222" header="0.511805555555556" footer="0.511805555555556"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
+  <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="0">
+    <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
+    <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
   </headerFooter>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_Histograms_xScale_93</xm:f>
+          </x14:formula1>
+          <xm:sqref>J2:J1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_Histograms_FacetScale_96</xm:f>
+          </x14:formula1>
+          <xm:sqref>M2:M1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_Histograms_xScale_93</xm:f>
+          </x14:formula1>
+          <xm:sqref>J2:J1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_Histograms_FacetScale_96</xm:f>
+          </x14:formula1>
+          <xm:sqref>M2:M1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_Histograms_xScale_93</xm:f>
+          </x14:formula1>
+          <xm:sqref>J2:J1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_Histograms_FacetScale_96</xm:f>
+          </x14:formula1>
+          <xm:sqref>M2:M1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_axisScaleValues</xm:f>
+          </x14:formula1>
+          <xm:sqref>J2:J1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>validity_facetScaleValues</xm:f>
+          </x14:formula1>
+          <xm:sqref>M2:M1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
--- a/inst/templates/Reports.xlsx
+++ b/inst/templates/Reports.xlsx
@@ -707,14 +707,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999"/>
-        <bgColor rgb="FFE2F0D9"/>
+        <fgColor theme="9" tint="0.7999"/>
+        <bgColor rgb="FFFBE5D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.7999"/>
-        <bgColor rgb="FFFBE5D6"/>
+        <fgColor theme="5" tint="0.7999"/>
+        <bgColor rgb="FFE2F0D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -761,10 +761,6 @@
       <protection hidden="0" locked="0"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment textRotation="0" horizontal="center" vertical="bottom" indent="0"/>
-      <protection hidden="0" locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment textRotation="0" horizontal="center" vertical="bottom" indent="0" wrapText="1"/>
       <protection hidden="0" locked="0"/>
     </xf>
@@ -784,11 +780,15 @@
       <alignment textRotation="0" horizontal="general" vertical="bottom" indent="0" wrapText="1"/>
       <protection hidden="0" locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment textRotation="0" horizontal="center" vertical="bottom" indent="0" wrapText="1"/>
       <protection hidden="0" locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment textRotation="0" horizontal="center" vertical="bottom" indent="0"/>
+      <protection hidden="0" locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment textRotation="0" horizontal="general" vertical="bottom" indent="0"/>
       <protection hidden="0" locked="0"/>
     </xf>
@@ -1101,13 +1101,13 @@
   </cols>
   <sheetData>
     <row r="1" ht="23.25" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>56</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -1116,37 +1116,37 @@
       <c r="E1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="N1" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="O1" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="P1" s="8" t="s">
         <v>73</v>
       </c>
       <c r="Q1" s="15"/>
@@ -1158,7 +1158,7 @@
       <c r="A2" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -1327,72 +1327,6 @@
     <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
   </headerFooter>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_DistributionVsRange_ModeOfBinning_106</xm:f>
-          </x14:formula1>
-          <xm:sqref>J2:J1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_DistributionVsRange_yScale_109</xm:f>
-          </x14:formula1>
-          <xm:sqref>M2:M1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_DistributionVsRange_FacetScale_112</xm:f>
-          </x14:formula1>
-          <xm:sqref>P2:P1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_DistributionVsRange_ModeOfBinning_106</xm:f>
-          </x14:formula1>
-          <xm:sqref>J2:J1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_DistributionVsRange_yScale_109</xm:f>
-          </x14:formula1>
-          <xm:sqref>M2:M1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_DistributionVsRange_FacetScale_112</xm:f>
-          </x14:formula1>
-          <xm:sqref>P2:P1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_DistributionVsRange_ModeOfBinning_106</xm:f>
-          </x14:formula1>
-          <xm:sqref>J2:J1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_DistributionVsRange_yScale_109</xm:f>
-          </x14:formula1>
-          <xm:sqref>M2:M1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_DistributionVsRange_FacetScale_112</xm:f>
-          </x14:formula1>
-          <xm:sqref>P2:P1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
@@ -1435,13 +1369,13 @@
   </cols>
   <sheetData>
     <row r="1" ht="23.25" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>56</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -1459,7 +1393,7 @@
       <c r="H1" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1467,7 +1401,7 @@
       <c r="A2" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -1765,36 +1699,6 @@
     <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
   </headerFooter>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_DataGroups_Shape_10</xm:f>
-          </x14:formula1>
-          <xm:sqref>G2:G1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_DataGroups_Shape_10</xm:f>
-          </x14:formula1>
-          <xm:sqref>G2:G1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_DataGroups_Shape_10</xm:f>
-          </x14:formula1>
-          <xm:sqref>G2:G1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
@@ -2024,13 +1928,13 @@
   </cols>
   <sheetData>
     <row r="1" ht="45" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>56</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -2048,22 +1952,22 @@
       <c r="H1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" s="9" t="s">
         <v>63</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="N1" s="8" t="s">
         <v>66</v>
       </c>
       <c r="O1" s="1" t="s">
@@ -2075,43 +1979,43 @@
       <c r="Q1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="R1" s="9" t="s">
+      <c r="R1" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="S1" s="9" t="s">
+      <c r="S1" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="T1" s="9" t="s">
+      <c r="T1" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="U1" s="9" t="s">
+      <c r="U1" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="V1" s="9" t="s">
+      <c r="V1" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="W1" s="9" t="s">
+      <c r="W1" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="X1" s="9" t="s">
+      <c r="X1" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="Y1" s="9" t="s">
+      <c r="Y1" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="Z1" s="9" t="s">
+      <c r="Z1" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="AA1" s="9" t="s">
+      <c r="AA1" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="AB1" s="9" t="s">
+      <c r="AB1" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="AC1" s="9" t="s">
+      <c r="AC1" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="AD1" s="9" t="s">
+      <c r="AD1" s="8" t="s">
         <v>82</v>
       </c>
     </row>
@@ -2119,7 +2023,7 @@
       <c r="A2" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -2146,13 +2050,13 @@
       <c r="J2" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="K2" s="12" t="s">
+      <c r="K2" s="11" t="s">
         <v>93</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="M2" s="11" t="s">
         <v>95</v>
       </c>
       <c r="N2" s="2" t="s">
@@ -2167,7 +2071,7 @@
       <c r="Q2" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="R2" s="12" t="s">
+      <c r="R2" s="11" t="s">
         <v>100</v>
       </c>
       <c r="S2" s="2" t="s">
@@ -2208,9 +2112,9 @@
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
       <c r="R3" s="7"/>
       <c r="S3" s="7"/>
       <c r="T3" s="7"/>
@@ -2408,180 +2312,6 @@
     <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
   </headerFooter>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="9">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_TimeProfiles_yScale_38</xm:f>
-          </x14:formula1>
-          <xm:sqref>R2:R1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_TimeProfiles_SplitPlotsPerTimeRange_39</xm:f>
-          </x14:formula1>
-          <xm:sqref>S2:S1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_TimeProfiles_FacetScale_41</xm:f>
-          </x14:formula1>
-          <xm:sqref>U2:U1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_TimeProfiles_Plot_TimeProfiles_42</xm:f>
-          </x14:formula1>
-          <xm:sqref>V2:V1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_TimeProfiles_Plot_PredictedVsObserved_45</xm:f>
-          </x14:formula1>
-          <xm:sqref>Y2:Y1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_TimeProfiles_Plot_ResidualsAsHistogram_47</xm:f>
-          </x14:formula1>
-          <xm:sqref>AA2:AA1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_TimeProfiles_Plot_ResidualsVsTime_48</xm:f>
-          </x14:formula1>
-          <xm:sqref>AB2:AB1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_TimeProfiles_Plot_ResidualsVsObserved_49</xm:f>
-          </x14:formula1>
-          <xm:sqref>AC2:AC1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_TimeProfiles_Plot_QQ_50</xm:f>
-          </x14:formula1>
-          <xm:sqref>AD2:AD1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="9">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_TimeProfiles_yScale_38</xm:f>
-          </x14:formula1>
-          <xm:sqref>R2:R1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_TimeProfiles_SplitPlotsPerTimeRange_39</xm:f>
-          </x14:formula1>
-          <xm:sqref>S2:S1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_TimeProfiles_FacetScale_41</xm:f>
-          </x14:formula1>
-          <xm:sqref>U2:U1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_TimeProfiles_Plot_TimeProfiles_42</xm:f>
-          </x14:formula1>
-          <xm:sqref>V2:V1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_TimeProfiles_Plot_PredictedVsObserved_45</xm:f>
-          </x14:formula1>
-          <xm:sqref>Y2:Y1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_TimeProfiles_Plot_ResidualsAsHistogram_47</xm:f>
-          </x14:formula1>
-          <xm:sqref>AA2:AA1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_TimeProfiles_Plot_ResidualsVsTime_48</xm:f>
-          </x14:formula1>
-          <xm:sqref>AB2:AB1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_TimeProfiles_Plot_ResidualsVsObserved_49</xm:f>
-          </x14:formula1>
-          <xm:sqref>AC2:AC1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_TimeProfiles_Plot_QQ_50</xm:f>
-          </x14:formula1>
-          <xm:sqref>AD2:AD1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="9">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_TimeProfiles_yScale_38</xm:f>
-          </x14:formula1>
-          <xm:sqref>R2:R1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_TimeProfiles_SplitPlotsPerTimeRange_39</xm:f>
-          </x14:formula1>
-          <xm:sqref>S2:S1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_TimeProfiles_FacetScale_41</xm:f>
-          </x14:formula1>
-          <xm:sqref>U2:U1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_TimeProfiles_Plot_TimeProfiles_42</xm:f>
-          </x14:formula1>
-          <xm:sqref>V2:V1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_TimeProfiles_Plot_PredictedVsObserved_45</xm:f>
-          </x14:formula1>
-          <xm:sqref>Y2:Y1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_TimeProfiles_Plot_ResidualsAsHistogram_47</xm:f>
-          </x14:formula1>
-          <xm:sqref>AA2:AA1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_TimeProfiles_Plot_ResidualsVsTime_48</xm:f>
-          </x14:formula1>
-          <xm:sqref>AB2:AB1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_TimeProfiles_Plot_ResidualsVsObserved_49</xm:f>
-          </x14:formula1>
-          <xm:sqref>AC2:AC1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_TimeProfiles_Plot_QQ_50</xm:f>
-          </x14:formula1>
-          <xm:sqref>AD2:AD1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="9">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
@@ -2752,13 +2482,13 @@
   </cols>
   <sheetData>
     <row r="1" ht="23.25" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>56</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -2767,34 +2497,34 @@
       <c r="E1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="8" t="s">
         <v>129</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="N1" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="O1" s="8" t="s">
         <v>131</v>
       </c>
     </row>
@@ -2802,7 +2532,7 @@
       <c r="A2" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -2967,90 +2697,6 @@
     <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
   </headerFooter>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_PKParameter_Boxplot_yScale_64</xm:f>
-          </x14:formula1>
-          <xm:sqref>J2:J1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_PKParameter_Boxplot_FacetScale_67</xm:f>
-          </x14:formula1>
-          <xm:sqref>M2:M1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_PKParameter_Boxplot_Plot_Absolute_68</xm:f>
-          </x14:formula1>
-          <xm:sqref>N2:N1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_PKParameter_Boxplot_Plot_Ratio_69</xm:f>
-          </x14:formula1>
-          <xm:sqref>O2:O1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_PKParameter_Boxplot_yScale_64</xm:f>
-          </x14:formula1>
-          <xm:sqref>J2:J1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_PKParameter_Boxplot_FacetScale_67</xm:f>
-          </x14:formula1>
-          <xm:sqref>M2:M1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_PKParameter_Boxplot_Plot_Absolute_68</xm:f>
-          </x14:formula1>
-          <xm:sqref>N2:N1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_PKParameter_Boxplot_Plot_Ratio_69</xm:f>
-          </x14:formula1>
-          <xm:sqref>O2:O1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_PKParameter_Boxplot_yScale_64</xm:f>
-          </x14:formula1>
-          <xm:sqref>J2:J1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_PKParameter_Boxplot_FacetScale_67</xm:f>
-          </x14:formula1>
-          <xm:sqref>M2:M1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_PKParameter_Boxplot_Plot_Absolute_68</xm:f>
-          </x14:formula1>
-          <xm:sqref>N2:N1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_PKParameter_Boxplot_Plot_Ratio_69</xm:f>
-          </x14:formula1>
-          <xm:sqref>O2:O1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
@@ -3105,13 +2751,13 @@
   </cols>
   <sheetData>
     <row r="1" ht="23.25" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>56</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -3123,28 +2769,28 @@
       <c r="F1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="8" t="s">
         <v>129</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>61</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="N1" s="8" t="s">
         <v>73</v>
       </c>
     </row>
@@ -3152,7 +2798,7 @@
       <c r="A2" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -3314,54 +2960,6 @@
     <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
   </headerFooter>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_PKParameter_Forest_xScale_80</xm:f>
-          </x14:formula1>
-          <xm:sqref>K2:K1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_PKParameter_Forest_FacetScale_83</xm:f>
-          </x14:formula1>
-          <xm:sqref>N2:N1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_PKParameter_Forest_xScale_80</xm:f>
-          </x14:formula1>
-          <xm:sqref>K2:K1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_PKParameter_Forest_FacetScale_83</xm:f>
-          </x14:formula1>
-          <xm:sqref>N2:N1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_PKParameter_Forest_xScale_80</xm:f>
-          </x14:formula1>
-          <xm:sqref>K2:K1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_PKParameter_Forest_FacetScale_83</xm:f>
-          </x14:formula1>
-          <xm:sqref>N2:N1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
@@ -3406,13 +3004,13 @@
   </cols>
   <sheetData>
     <row r="1" ht="23.25" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>56</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -3421,28 +3019,28 @@
       <c r="E1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="8" t="s">
         <v>73</v>
       </c>
       <c r="N1" s="15"/>
@@ -3457,7 +3055,7 @@
       <c r="A2" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
         <v>84</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -3620,54 +3218,6 @@
     <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
   </headerFooter>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_Histograms_xScale_93</xm:f>
-          </x14:formula1>
-          <xm:sqref>J2:J1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_Histograms_FacetScale_96</xm:f>
-          </x14:formula1>
-          <xm:sqref>M2:M1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_Histograms_xScale_93</xm:f>
-          </x14:formula1>
-          <xm:sqref>J2:J1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_Histograms_FacetScale_96</xm:f>
-          </x14:formula1>
-          <xm:sqref>M2:M1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_Histograms_xScale_93</xm:f>
-          </x14:formula1>
-          <xm:sqref>J2:J1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>validity_Histograms_FacetScale_96</xm:f>
-          </x14:formula1>
-          <xm:sqref>M2:M1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
